--- a/medical_application_forms/025_child_medical_care_authorization_form--medical_application_forms.xlsx
+++ b/medical_application_forms/025_child_medical_care_authorization_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,8 +939,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,12 +968,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'legal_guardian',_'value':_'guardian'}</t>
+          <t>legal_guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Legal Guardian', 'value': 'guardian'}</t>
+          <t>Legal Guardian</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'court_appointed_custodian',_'value':_'custodian'}</t>
+          <t>court_appointed_custodian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Court Appointed Custodian', 'value': 'custodian'}</t>
+          <t>Court Appointed Custodian</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_grant_authorization',_'value':_true}</t>
+          <t>i_grant_authorization</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I Grant Authorization', 'value': True}</t>
+          <t>I Grant Authorization</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_decline_authorization',_'value':_false}</t>
+          <t>i_decline_authorization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I Decline Authorization', 'value': False}</t>
+          <t>I Decline Authorization</t>
         </is>
       </c>
     </row>
